--- a/IPC_Producto.xlsx
+++ b/IPC_Producto.xlsx
@@ -1874,13 +1874,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2">
-        <v>0.005072919757273551</v>
+        <v>0.005072919757273552</v>
       </c>
       <c r="D2" s="2">
         <v>111.9282710626499</v>
       </c>
       <c r="E2" s="2">
-        <v>0.005072919757273548</v>
+        <v>0.005072919757273552</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1897,7 +1897,7 @@
         <v>106.1498940178463</v>
       </c>
       <c r="E3" s="2">
-        <v>0.008859973316911688</v>
+        <v>0.008859973316911691</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1914,7 +1914,7 @@
         <v>117.4203143698698</v>
       </c>
       <c r="E4" s="2">
-        <v>0.002546220001030065</v>
+        <v>0.002546220001030067</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1931,7 +1931,7 @@
         <v>140.9902884920846</v>
       </c>
       <c r="E5" s="2">
-        <v>0.009282095859673435</v>
+        <v>0.009282095859673439</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1942,13 +1942,13 @@
         <v>14</v>
       </c>
       <c r="C6" s="2">
-        <v>0.0007010018574070695</v>
+        <v>0.0007010018574070696</v>
       </c>
       <c r="D6" s="2">
         <v>112.8058450279853</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0007010018574070692</v>
+        <v>0.0007010018574070696</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1965,7 +1965,7 @@
         <v>125.6234452640111</v>
       </c>
       <c r="E7" s="2">
-        <v>0.003005188036129284</v>
+        <v>0.003005188036129286</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1982,7 +1982,7 @@
         <v>105.8479322173094</v>
       </c>
       <c r="E8" s="2">
-        <v>0.002884253931072554</v>
+        <v>0.002884253931072556</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1999,7 +1999,7 @@
         <v>139.5419380871918</v>
       </c>
       <c r="E9" s="2">
-        <v>0.002048146934569707</v>
+        <v>0.002048146934569708</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2016,7 +2016,7 @@
         <v>111.5953304281922</v>
       </c>
       <c r="E10" s="2">
-        <v>0.003510574179099659</v>
+        <v>0.00351057417909966</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2033,7 +2033,7 @@
         <v>106.2118929662147</v>
       </c>
       <c r="E11" s="2">
-        <v>0.007356002648904156</v>
+        <v>0.007356002648904159</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2044,13 +2044,13 @@
         <v>26</v>
       </c>
       <c r="C12" s="2">
-        <v>0.008244376947752059</v>
+        <v>0.008244376947752057</v>
       </c>
       <c r="D12" s="2">
         <v>124.1158799086609</v>
       </c>
       <c r="E12" s="2">
-        <v>0.008244376947752055</v>
+        <v>0.008244376947752057</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2061,13 +2061,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="2">
-        <v>0.007037472301629747</v>
+        <v>0.007037472301629746</v>
       </c>
       <c r="D13" s="2">
         <v>128.289220318164</v>
       </c>
       <c r="E13" s="2">
-        <v>0.007037472301629743</v>
+        <v>0.007037472301629746</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2084,7 +2084,7 @@
         <v>102.5418177078101</v>
       </c>
       <c r="E14" s="2">
-        <v>0.005417519287638285</v>
+        <v>0.005417519287638287</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2101,7 +2101,7 @@
         <v>109.8971467464251</v>
       </c>
       <c r="E15" s="2">
-        <v>0.006266820980786545</v>
+        <v>0.006266820980786548</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2112,13 +2112,13 @@
         <v>34</v>
       </c>
       <c r="C16" s="2">
-        <v>0.004436722185375188</v>
+        <v>0.004436722185375187</v>
       </c>
       <c r="D16" s="2">
         <v>111.0614294282107</v>
       </c>
       <c r="E16" s="2">
-        <v>0.004436722185375186</v>
+        <v>0.004436722185375187</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2135,7 +2135,7 @@
         <v>130.7509088604343</v>
       </c>
       <c r="E17" s="2">
-        <v>0.004842631964663094</v>
+        <v>0.004842631964663096</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2152,7 +2152,7 @@
         <v>118.6132825202857</v>
       </c>
       <c r="E18" s="2">
-        <v>0.0005071907989218153</v>
+        <v>0.0005071907989218156</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2163,13 +2163,13 @@
         <v>40</v>
       </c>
       <c r="C19" s="2">
-        <v>0.00578336671593761</v>
+        <v>0.005783366715937609</v>
       </c>
       <c r="D19" s="2">
         <v>123.1052954193234</v>
       </c>
       <c r="E19" s="2">
-        <v>0.005783366715937608</v>
+        <v>0.005783366715937609</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2186,7 +2186,7 @@
         <v>115.4640245409252</v>
       </c>
       <c r="E20" s="2">
-        <v>0.01479781560049318</v>
+        <v>0.01479781560049319</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2203,7 +2203,7 @@
         <v>115.5453176953734</v>
       </c>
       <c r="E21" s="2">
-        <v>0.003930085552013755</v>
+        <v>0.003930085552013757</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2220,7 +2220,7 @@
         <v>106.3227618631567</v>
       </c>
       <c r="E22" s="2">
-        <v>0.00326015820699353</v>
+        <v>0.003260158206993532</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2237,7 +2237,7 @@
         <v>115.4640245409252</v>
       </c>
       <c r="E23" s="2">
-        <v>0.0009989057206363603</v>
+        <v>0.0009989057206363607</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2254,7 +2254,7 @@
         <v>108.8633114644669</v>
       </c>
       <c r="E24" s="2">
-        <v>0.003523276456239611</v>
+        <v>0.003523276456239613</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2265,13 +2265,13 @@
         <v>52</v>
       </c>
       <c r="C25" s="2">
-        <v>0.003695532390379333</v>
+        <v>0.003695532390379334</v>
       </c>
       <c r="D25" s="2">
         <v>109.224768253359</v>
       </c>
       <c r="E25" s="2">
-        <v>0.003695532390379331</v>
+        <v>0.003695532390379334</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2288,7 +2288,7 @@
         <v>108.2263005771217</v>
       </c>
       <c r="E26" s="2">
-        <v>0.001584224655179124</v>
+        <v>0.001584224655179125</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2305,7 +2305,7 @@
         <v>104.7451032421541</v>
       </c>
       <c r="E27" s="2">
-        <v>0.001695490530041117</v>
+        <v>0.001695490530041118</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2322,7 +2322,7 @@
         <v>104.7451032421541</v>
       </c>
       <c r="E28" s="2">
-        <v>0.003570673763680799</v>
+        <v>0.003570673763680801</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2339,7 +2339,7 @@
         <v>108.2263005771217</v>
       </c>
       <c r="E29" s="2">
-        <v>0.009767041184025767</v>
+        <v>0.009767041184025773</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2356,7 +2356,7 @@
         <v>108.2263005771217</v>
       </c>
       <c r="E30" s="2">
-        <v>0.009460282350640113</v>
+        <v>0.009460282350640116</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2367,13 +2367,13 @@
         <v>64</v>
       </c>
       <c r="C31" s="2">
-        <v>0.005721464151447787</v>
+        <v>0.005721464151447786</v>
       </c>
       <c r="D31" s="2">
         <v>103.175326053323</v>
       </c>
       <c r="E31" s="2">
-        <v>0.005721464151447785</v>
+        <v>0.005721464151447786</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2384,13 +2384,13 @@
         <v>66</v>
       </c>
       <c r="C32" s="2">
-        <v>0.00737547904341639</v>
+        <v>0.007375479043416391</v>
       </c>
       <c r="D32" s="2">
         <v>117.6733433869076</v>
       </c>
       <c r="E32" s="2">
-        <v>0.007375479043416387</v>
+        <v>0.007375479043416391</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2424,7 +2424,7 @@
         <v>105.2963892644546</v>
       </c>
       <c r="E34" s="2">
-        <v>0.002705111852130708</v>
+        <v>0.002705111852130709</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2441,7 +2441,7 @@
         <v>110.1410655650722</v>
       </c>
       <c r="E35" s="2">
-        <v>0.007473307906729006</v>
+        <v>0.00747330790672901</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2452,13 +2452,13 @@
         <v>74</v>
       </c>
       <c r="C36" s="2">
-        <v>0.003420198450036595</v>
+        <v>0.003420198450036596</v>
       </c>
       <c r="D36" s="2">
         <v>117.3100636453181</v>
       </c>
       <c r="E36" s="2">
-        <v>0.003420198450036593</v>
+        <v>0.003420198450036596</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2469,13 +2469,13 @@
         <v>76</v>
       </c>
       <c r="C37" s="2">
-        <v>0.009296595673755003</v>
+        <v>0.009296595673755001</v>
       </c>
       <c r="D37" s="2">
         <v>107.5905370439684</v>
       </c>
       <c r="E37" s="2">
-        <v>0.009296595673754999</v>
+        <v>0.009296595673755001</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2492,7 +2492,7 @@
         <v>102.940541699567</v>
       </c>
       <c r="E38" s="2">
-        <v>0.008647441386851015</v>
+        <v>0.008647441386851019</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2509,7 +2509,7 @@
         <v>141.9054776913475</v>
       </c>
       <c r="E39" s="2">
-        <v>0.00134466263269796</v>
+        <v>0.001344662632697961</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2526,7 +2526,7 @@
         <v>118.275988996903</v>
       </c>
       <c r="E40" s="2">
-        <v>0.001281571696265561</v>
+        <v>0.001281571696265562</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2537,13 +2537,13 @@
         <v>84</v>
       </c>
       <c r="C41" s="2">
-        <v>0.003865794805332887</v>
+        <v>0.003865794805332888</v>
       </c>
       <c r="D41" s="2">
         <v>110.6185748351489</v>
       </c>
       <c r="E41" s="2">
-        <v>0.003865794805332886</v>
+        <v>0.003865794805332888</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2560,7 +2560,7 @@
         <v>112.7549908247973</v>
       </c>
       <c r="E42" s="2">
-        <v>0.0007394912271096143</v>
+        <v>0.0007394912271096146</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2577,7 +2577,7 @@
         <v>147.0733031615884</v>
       </c>
       <c r="E43" s="2">
-        <v>0.0008425152421623412</v>
+        <v>0.0008425152421623416</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2594,7 +2594,7 @@
         <v>113.6655973554545</v>
       </c>
       <c r="E44" s="2">
-        <v>0.001542812596938845</v>
+        <v>0.001542812596938846</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2611,7 +2611,7 @@
         <v>113.6270523328692</v>
       </c>
       <c r="E45" s="2">
-        <v>0.002465189260774157</v>
+        <v>0.002465189260774158</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2628,7 +2628,7 @@
         <v>121.6849944029754</v>
       </c>
       <c r="E46" s="2">
-        <v>0.002621123712812742</v>
+        <v>0.002621123712812744</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2645,7 +2645,7 @@
         <v>104.042795975193</v>
       </c>
       <c r="E47" s="2">
-        <v>0.002713967133811539</v>
+        <v>0.00271396713381154</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2679,7 +2679,7 @@
         <v>106.1498940178463</v>
       </c>
       <c r="E49" s="2">
-        <v>0.0005639815215154372</v>
+        <v>0.0005639815215154375</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2690,13 +2690,13 @@
         <v>102</v>
       </c>
       <c r="C50" s="2">
-        <v>0.0005976073345263595</v>
+        <v>0.0005976073345263596</v>
       </c>
       <c r="D50" s="2">
         <v>109.4975649016668</v>
       </c>
       <c r="E50" s="2">
-        <v>0.0005976073345263593</v>
+        <v>0.0005976073345263596</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2710,10 +2710,10 @@
         <v>0.003270998656326806</v>
       </c>
       <c r="D51" s="2">
-        <v>118.3826588431147</v>
+        <v>118.3826588431146</v>
       </c>
       <c r="E51" s="2">
-        <v>0.003270998656326804</v>
+        <v>0.003270998656326806</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2730,7 +2730,7 @@
         <v>107.2731238009294</v>
       </c>
       <c r="E52" s="2">
-        <v>0.001955201620551648</v>
+        <v>0.001955201620551649</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2741,13 +2741,13 @@
         <v>108</v>
       </c>
       <c r="C53" s="2">
-        <v>0.002218327229142887</v>
+        <v>0.002218327229142888</v>
       </c>
       <c r="D53" s="2">
         <v>106.3548870527349</v>
       </c>
       <c r="E53" s="2">
-        <v>0.002218327229142886</v>
+        <v>0.002218327229142888</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2764,7 +2764,7 @@
         <v>105.8793735771382</v>
       </c>
       <c r="E54" s="2">
-        <v>0.002088889304883563</v>
+        <v>0.002088889304883564</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2775,13 +2775,13 @@
         <v>112</v>
       </c>
       <c r="C55" s="2">
-        <v>0.004871767549653516</v>
+        <v>0.004871767549653517</v>
       </c>
       <c r="D55" s="2">
         <v>121.444736749867</v>
       </c>
       <c r="E55" s="2">
-        <v>0.004871767549653514</v>
+        <v>0.004871767549653517</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2798,7 +2798,7 @@
         <v>126.525520444729</v>
       </c>
       <c r="E56" s="2">
-        <v>0.002628894483991281</v>
+        <v>0.002628894483991282</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2832,7 +2832,7 @@
         <v>101.2542268572998</v>
       </c>
       <c r="E58" s="2">
-        <v>0.002339898716853271</v>
+        <v>0.002339898716853272</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2849,7 +2849,7 @@
         <v>103.324115002149</v>
       </c>
       <c r="E59" s="2">
-        <v>0.001378070884121193</v>
+        <v>0.001378070884121194</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2866,7 +2866,7 @@
         <v>145.4023667235494</v>
       </c>
       <c r="E60" s="2">
-        <v>0.0035363398118925</v>
+        <v>0.003536339811892501</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2883,7 +2883,7 @@
         <v>137.5744600273334</v>
       </c>
       <c r="E61" s="2">
-        <v>0.003607950371015537</v>
+        <v>0.003607950371015539</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2911,13 +2911,13 @@
         <v>128</v>
       </c>
       <c r="C63" s="2">
-        <v>0.0141924696763751</v>
+        <v>0.01419246967637511</v>
       </c>
       <c r="D63" s="2">
         <v>106.7500758657324</v>
       </c>
       <c r="E63" s="2">
-        <v>0.0141924696763751</v>
+        <v>0.01419246967637511</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2934,7 +2934,7 @@
         <v>106.0534301652215</v>
       </c>
       <c r="E64" s="2">
-        <v>0.00823555398520092</v>
+        <v>0.008235553985200924</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2951,7 +2951,7 @@
         <v>115.3743905726049</v>
       </c>
       <c r="E65" s="2">
-        <v>0.001068703530255677</v>
+        <v>0.001068703530255678</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2962,7 +2962,7 @@
         <v>134</v>
       </c>
       <c r="C66" s="2">
-        <v>0.001677361727325672</v>
+        <v>0.001677361727325671</v>
       </c>
       <c r="D66" s="2">
         <v>114.1180631779598</v>
@@ -2985,7 +2985,7 @@
         <v>104.7451032421541</v>
       </c>
       <c r="E67" s="2">
-        <v>0.003033920776832151</v>
+        <v>0.003033920776832152</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3002,7 +3002,7 @@
         <v>104.1409961750541</v>
       </c>
       <c r="E68" s="2">
-        <v>0.001920698205787818</v>
+        <v>0.001920698205787819</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3013,13 +3013,13 @@
         <v>140</v>
       </c>
       <c r="C69" s="2">
-        <v>0.001829311596817195</v>
+        <v>0.001829311596817196</v>
       </c>
       <c r="D69" s="2">
         <v>125.6420830245765</v>
       </c>
       <c r="E69" s="2">
-        <v>0.001829311596817194</v>
+        <v>0.001829311596817196</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3036,7 +3036,7 @@
         <v>106.6623762157959</v>
       </c>
       <c r="E70" s="2">
-        <v>0.0004534060770302529</v>
+        <v>0.0004534060770302531</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -3053,7 +3053,7 @@
         <v>111.0031885489291</v>
       </c>
       <c r="E71" s="2">
-        <v>0.00128776698371726</v>
+        <v>0.001287766983717261</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -3070,7 +3070,7 @@
         <v>107.7493608535859</v>
       </c>
       <c r="E72" s="2">
-        <v>0.002878730579439936</v>
+        <v>0.002878730579439938</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -3087,7 +3087,7 @@
         <v>139.3014956247881</v>
       </c>
       <c r="E73" s="2">
-        <v>0.002364321672286093</v>
+        <v>0.002364321672286094</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -3104,7 +3104,7 @@
         <v>118.2386630878814</v>
       </c>
       <c r="E74" s="2">
-        <v>0.0002937358646575451</v>
+        <v>0.0002937358646575452</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -3115,13 +3115,13 @@
         <v>152</v>
       </c>
       <c r="C75" s="2">
-        <v>0.001122218697205914</v>
+        <v>0.001122218697205915</v>
       </c>
       <c r="D75" s="2">
         <v>129.0018921199543</v>
       </c>
       <c r="E75" s="2">
-        <v>0.001122218697205914</v>
+        <v>0.001122218697205915</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -3138,7 +3138,7 @@
         <v>125.5916111746146</v>
       </c>
       <c r="E76" s="2">
-        <v>0.001465842911871495</v>
+        <v>0.001465842911871496</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -3155,7 +3155,7 @@
         <v>114.9766663232567</v>
       </c>
       <c r="E77" s="2">
-        <v>0.003552437559175311</v>
+        <v>0.003552437559175313</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -3183,13 +3183,13 @@
         <v>160</v>
       </c>
       <c r="C79" s="2">
-        <v>0.00280502907343414</v>
+        <v>0.002805029073434139</v>
       </c>
       <c r="D79" s="2">
-        <v>146.1206693113605</v>
+        <v>146.1206693113606</v>
       </c>
       <c r="E79" s="2">
-        <v>0.002805029073434138</v>
+        <v>0.002805029073434139</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -3200,13 +3200,13 @@
         <v>162</v>
       </c>
       <c r="C80" s="2">
-        <v>0.007733863743391152</v>
+        <v>0.007733863743391153</v>
       </c>
       <c r="D80" s="2">
         <v>114.5242676634957</v>
       </c>
       <c r="E80" s="2">
-        <v>0.007733863743391149</v>
+        <v>0.007733863743391153</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -3223,7 +3223,7 @@
         <v>129.8922997094498</v>
       </c>
       <c r="E81" s="2">
-        <v>0.002582974876055801</v>
+        <v>0.002582974876055803</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -3240,7 +3240,7 @@
         <v>123.1052954193234</v>
       </c>
       <c r="E82" s="2">
-        <v>0.002160310127228293</v>
+        <v>0.002160310127228294</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -3257,7 +3257,7 @@
         <v>103.2369389449865</v>
       </c>
       <c r="E83" s="2">
-        <v>0.003722325944605069</v>
+        <v>0.003722325944605071</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -3274,7 +3274,7 @@
         <v>134.1420093196151</v>
       </c>
       <c r="E84" s="2">
-        <v>0.02093543796076693</v>
+        <v>0.02093543796076694</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -3291,7 +3291,7 @@
         <v>117.0935057238577</v>
       </c>
       <c r="E85" s="2">
-        <v>0.002394938600945776</v>
+        <v>0.002394938600945777</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -3308,7 +3308,7 @@
         <v>102.2372593471163</v>
       </c>
       <c r="E86" s="2">
-        <v>0.007819150681015625</v>
+        <v>0.007819150681015628</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -3325,7 +3325,7 @@
         <v>120.0456852000133</v>
       </c>
       <c r="E87" s="2">
-        <v>0.002894931288376156</v>
+        <v>0.002894931288376157</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -3342,7 +3342,7 @@
         <v>117.8045668030035</v>
       </c>
       <c r="E88" s="2">
-        <v>0.002699615523884322</v>
+        <v>0.002699615523884324</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -3359,7 +3359,7 @@
         <v>110.6604814709728</v>
       </c>
       <c r="E89" s="2">
-        <v>0.003400333230631694</v>
+        <v>0.003400333230631696</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -3370,13 +3370,13 @@
         <v>182</v>
       </c>
       <c r="C90" s="2">
-        <v>0.003962330850707712</v>
+        <v>0.003962330850707713</v>
       </c>
       <c r="D90" s="2">
         <v>125.6234452640111</v>
       </c>
       <c r="E90" s="2">
-        <v>0.00396233085070771</v>
+        <v>0.003962330850707713</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -3393,7 +3393,7 @@
         <v>126.0862481638212</v>
       </c>
       <c r="E91" s="2">
-        <v>0.002998510244311585</v>
+        <v>0.002998510244311586</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -3410,7 +3410,7 @@
         <v>111.1516115143998</v>
       </c>
       <c r="E92" s="2">
-        <v>0.00168744673143262</v>
+        <v>0.001687446731432621</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -3427,7 +3427,7 @@
         <v>109.1195949990192</v>
       </c>
       <c r="E93" s="2">
-        <v>0.004121292801148047</v>
+        <v>0.004121292801148048</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -3444,7 +3444,7 @@
         <v>107.401724883425</v>
       </c>
       <c r="E94" s="2">
-        <v>0.00132490817464119</v>
+        <v>0.001324908174641191</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -3478,7 +3478,7 @@
         <v>120.7050459353101</v>
       </c>
       <c r="E96" s="2">
-        <v>0.003658040834499997</v>
+        <v>0.003658040834499999</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -3495,7 +3495,7 @@
         <v>100.7685614543961</v>
       </c>
       <c r="E97" s="2">
-        <v>0.006703068699049615</v>
+        <v>0.006703068699049618</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -3506,7 +3506,7 @@
         <v>198</v>
       </c>
       <c r="C98" s="2">
-        <v>0.002294404390508186</v>
+        <v>0.002294404390508185</v>
       </c>
       <c r="D98" s="2">
         <v>106.5600880005262</v>
@@ -3529,7 +3529,7 @@
         <v>106.555680005594</v>
       </c>
       <c r="E99" s="2">
-        <v>0.006160681671188749</v>
+        <v>0.006160681671188752</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -3563,7 +3563,7 @@
         <v>112.0670064337469</v>
       </c>
       <c r="E101" s="2">
-        <v>0.004357442714277669</v>
+        <v>0.00435744271427767</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -3580,7 +3580,7 @@
         <v>115.7893115573132</v>
       </c>
       <c r="E102" s="2">
-        <v>0.003771650412011105</v>
+        <v>0.003771650412011106</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -3591,13 +3591,13 @@
         <v>208</v>
       </c>
       <c r="C103" s="2">
-        <v>0.0005810605370138633</v>
+        <v>0.0005810605370138634</v>
       </c>
       <c r="D103" s="2">
         <v>119.058904154145</v>
       </c>
       <c r="E103" s="2">
-        <v>0.0005810605370138631</v>
+        <v>0.0005810605370138634</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -3614,7 +3614,7 @@
         <v>114.8955067785967</v>
       </c>
       <c r="E104" s="2">
-        <v>0.004516531196374417</v>
+        <v>0.004516531196374419</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -3625,13 +3625,13 @@
         <v>212</v>
       </c>
       <c r="C105" s="2">
-        <v>0.003443050487992029</v>
+        <v>0.003443050487992028</v>
       </c>
       <c r="D105" s="2">
         <v>117.7474264967052</v>
       </c>
       <c r="E105" s="2">
-        <v>0.003443050487992027</v>
+        <v>0.003443050487992028</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -3642,13 +3642,13 @@
         <v>214</v>
       </c>
       <c r="C106" s="2">
-        <v>0.003760086440344693</v>
+        <v>0.003760086440344694</v>
       </c>
       <c r="D106" s="2">
         <v>113.1862835115028</v>
       </c>
       <c r="E106" s="2">
-        <v>0.003760086440344691</v>
+        <v>0.003760086440344694</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -3659,13 +3659,13 @@
         <v>216</v>
       </c>
       <c r="C107" s="2">
-        <v>0.005373169264630402</v>
+        <v>0.005373169264630403</v>
       </c>
       <c r="D107" s="2">
         <v>117.0912311380369</v>
       </c>
       <c r="E107" s="2">
-        <v>0.0053731692646304</v>
+        <v>0.005373169264630403</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -3682,7 +3682,7 @@
         <v>111.5844671407855</v>
       </c>
       <c r="E108" s="2">
-        <v>0.0009622746621867884</v>
+        <v>0.0009622746621867889</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -3699,7 +3699,7 @@
         <v>113.7691972882364</v>
       </c>
       <c r="E109" s="2">
-        <v>0.003108102424353972</v>
+        <v>0.003108102424353974</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -3716,7 +3716,7 @@
         <v>104.1326212346158</v>
       </c>
       <c r="E110" s="2">
-        <v>0.004373945643484955</v>
+        <v>0.004373945643484957</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -3733,7 +3733,7 @@
         <v>102.5496308672514</v>
       </c>
       <c r="E111" s="2">
-        <v>0.003678143208814877</v>
+        <v>0.003678143208814879</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -3750,7 +3750,7 @@
         <v>107.0895152982296</v>
       </c>
       <c r="E112" s="2">
-        <v>0.003315778564766497</v>
+        <v>0.003315778564766498</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -3767,7 +3767,7 @@
         <v>115.824474374058</v>
       </c>
       <c r="E113" s="2">
-        <v>0.0009533443905715722</v>
+        <v>0.0009533443905715727</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -3784,7 +3784,7 @@
         <v>112.1474795502661</v>
       </c>
       <c r="E114" s="2">
-        <v>0.0005239080414722099</v>
+        <v>0.0005239080414722101</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -3795,7 +3795,7 @@
         <v>232</v>
       </c>
       <c r="C115" s="2">
-        <v>0.002247755450654817</v>
+        <v>0.002247755450654816</v>
       </c>
       <c r="D115" s="2">
         <v>109.8211612559688</v>
@@ -3812,13 +3812,13 @@
         <v>234</v>
       </c>
       <c r="C116" s="2">
-        <v>0.004287135021955557</v>
+        <v>0.004287135021955558</v>
       </c>
       <c r="D116" s="2">
         <v>140.1677028555776</v>
       </c>
       <c r="E116" s="2">
-        <v>0.004287135021955556</v>
+        <v>0.004287135021955558</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -3835,7 +3835,7 @@
         <v>130.3266217145816</v>
       </c>
       <c r="E117" s="2">
-        <v>0.002239187229884927</v>
+        <v>0.002239187229884928</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -3852,7 +3852,7 @@
         <v>122.5725893240119</v>
       </c>
       <c r="E118" s="2">
-        <v>0.0005641748576908799</v>
+        <v>0.0005641748576908801</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -3863,7 +3863,7 @@
         <v>240</v>
       </c>
       <c r="C119" s="2">
-        <v>0.003340150088683029</v>
+        <v>0.003340150088683028</v>
       </c>
       <c r="D119" s="2">
         <v>124.9914840788052</v>
@@ -3886,7 +3886,7 @@
         <v>103.4747290871829</v>
       </c>
       <c r="E120" s="2">
-        <v>0.003761360513208907</v>
+        <v>0.003761360513208909</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -3897,13 +3897,13 @@
         <v>244</v>
       </c>
       <c r="C121" s="2">
-        <v>0.003740799964779363</v>
+        <v>0.003740799964779362</v>
       </c>
       <c r="D121" s="2">
         <v>102.251517095731</v>
       </c>
       <c r="E121" s="2">
-        <v>0.003740799964779361</v>
+        <v>0.003740799964779362</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -3920,7 +3920,7 @@
         <v>103.1261071385626</v>
       </c>
       <c r="E122" s="2">
-        <v>0.001208482093582733</v>
+        <v>0.001208482093582734</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -3931,13 +3931,13 @@
         <v>248</v>
       </c>
       <c r="C123" s="2">
-        <v>0.0009354991845842223</v>
+        <v>0.0009354991845842224</v>
       </c>
       <c r="D123" s="2">
         <v>110.4612798948551</v>
       </c>
       <c r="E123" s="2">
-        <v>0.0009354991845842218</v>
+        <v>0.0009354991845842224</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -3954,7 +3954,7 @@
         <v>101.7612599821727</v>
       </c>
       <c r="E124" s="2">
-        <v>0.0003204143031132506</v>
+        <v>0.0003204143031132507</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -3971,7 +3971,7 @@
         <v>109.7888775361703</v>
       </c>
       <c r="E125" s="2">
-        <v>0.001790867665905952</v>
+        <v>0.001790867665905953</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -3988,7 +3988,7 @@
         <v>104.098689769006</v>
       </c>
       <c r="E126" s="2">
-        <v>0.001475921665927046</v>
+        <v>0.001475921665927047</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -4005,7 +4005,7 @@
         <v>104.7216466302614</v>
       </c>
       <c r="E127" s="2">
-        <v>0.002580486044842334</v>
+        <v>0.002580486044842335</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -4022,7 +4022,7 @@
         <v>100.4782512558394</v>
       </c>
       <c r="E128" s="2">
-        <v>0.001939948454066659</v>
+        <v>0.00193994845406666</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -4039,7 +4039,7 @@
         <v>100.9224454109563</v>
       </c>
       <c r="E129" s="2">
-        <v>0.003771942039398481</v>
+        <v>0.003771942039398483</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -4056,7 +4056,7 @@
         <v>100.5124992227335</v>
       </c>
       <c r="E130" s="2">
-        <v>0.002751028724926907</v>
+        <v>0.002751028724926908</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -4073,7 +4073,7 @@
         <v>103.176012008472</v>
       </c>
       <c r="E131" s="2">
-        <v>0.001166645516296617</v>
+        <v>0.001166645516296618</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -4090,7 +4090,7 @@
         <v>103.2500038791411</v>
       </c>
       <c r="E132" s="2">
-        <v>0.004009166584489964</v>
+        <v>0.004009166584489966</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -4107,7 +4107,7 @@
         <v>104.0271522891571</v>
       </c>
       <c r="E133" s="2">
-        <v>0.003524733599281062</v>
+        <v>0.003524733599281064</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -4124,7 +4124,7 @@
         <v>104.5340183659671</v>
       </c>
       <c r="E134" s="2">
-        <v>0.003946600864544815</v>
+        <v>0.003946600864544817</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -4141,7 +4141,7 @@
         <v>111.6446498032612</v>
       </c>
       <c r="E135" s="2">
-        <v>0.002072638011362967</v>
+        <v>0.002072638011362968</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -4158,7 +4158,7 @@
         <v>104.2979488676808</v>
       </c>
       <c r="E136" s="2">
-        <v>0.003220442762810589</v>
+        <v>0.00322044276281059</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -4175,7 +4175,7 @@
         <v>104.6241275631374</v>
       </c>
       <c r="E137" s="2">
-        <v>0.004720451181454747</v>
+        <v>0.004720451181454748</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -4192,7 +4192,7 @@
         <v>101.8754479966801</v>
       </c>
       <c r="E138" s="2">
-        <v>0.00376899947765727</v>
+        <v>0.003768999477657272</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -4226,7 +4226,7 @@
         <v>111.8441170141407</v>
       </c>
       <c r="E140" s="2">
-        <v>0.005548272871378738</v>
+        <v>0.005548272871378741</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -4243,7 +4243,7 @@
         <v>106.6521265845178</v>
       </c>
       <c r="E141" s="2">
-        <v>0.0008213413320196309</v>
+        <v>0.0008213413320196313</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -4260,7 +4260,7 @@
         <v>105.769687296315</v>
       </c>
       <c r="E142" s="2">
-        <v>0.00158831618795585</v>
+        <v>0.001588316187955851</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -4277,7 +4277,7 @@
         <v>101.4577216846236</v>
       </c>
       <c r="E143" s="2">
-        <v>0.003123825722659979</v>
+        <v>0.00312382572265998</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -4294,7 +4294,7 @@
         <v>114.3494643625409</v>
       </c>
       <c r="E144" s="2">
-        <v>0.001348600167820539</v>
+        <v>0.00134860016782054</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -4305,13 +4305,13 @@
         <v>292</v>
       </c>
       <c r="C145" s="2">
-        <v>0.002034092186191903</v>
+        <v>0.002034092186191904</v>
       </c>
       <c r="D145" s="2">
         <v>135.5285381220679</v>
       </c>
       <c r="E145" s="2">
-        <v>0.002034092186191903</v>
+        <v>0.002034092186191904</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -4328,7 +4328,7 @@
         <v>105.8071323082324</v>
       </c>
       <c r="E146" s="2">
-        <v>0.02534236687227568</v>
+        <v>0.02534236687227569</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -4339,13 +4339,13 @@
         <v>296</v>
       </c>
       <c r="C147" s="2">
-        <v>0.06465120339979126</v>
+        <v>0.06465120339979127</v>
       </c>
       <c r="D147" s="2">
         <v>111.713682362674</v>
       </c>
       <c r="E147" s="2">
-        <v>0.06465120339979123</v>
+        <v>0.06465120339979127</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -4379,7 +4379,7 @@
         <v>109.3496160875114</v>
       </c>
       <c r="E149" s="2">
-        <v>0.003281824256706082</v>
+        <v>0.003281824256706083</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -4396,7 +4396,7 @@
         <v>106.3486775626775</v>
       </c>
       <c r="E150" s="2">
-        <v>0.003387280493530314</v>
+        <v>0.003387280493530315</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -4413,7 +4413,7 @@
         <v>105.6623352597974</v>
       </c>
       <c r="E151" s="2">
-        <v>0.002319882539312561</v>
+        <v>0.002319882539312562</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -4430,7 +4430,7 @@
         <v>114.7191596702548</v>
       </c>
       <c r="E152" s="2">
-        <v>0.009869781760000005</v>
+        <v>0.00986978176000001</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -4441,13 +4441,13 @@
         <v>308</v>
       </c>
       <c r="C153" s="2">
-        <v>0.001016325943373207</v>
+        <v>0.001016325943373208</v>
       </c>
       <c r="D153" s="2">
         <v>130.7478489306803</v>
       </c>
       <c r="E153" s="2">
-        <v>0.001016325943373207</v>
+        <v>0.001016325943373208</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -4458,13 +4458,13 @@
         <v>310</v>
       </c>
       <c r="C154" s="2">
-        <v>0.006406330918587829</v>
+        <v>0.006406330918587828</v>
       </c>
       <c r="D154" s="2">
         <v>124.1447056278176</v>
       </c>
       <c r="E154" s="2">
-        <v>0.006406330918587826</v>
+        <v>0.006406330918587828</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -4481,7 +4481,7 @@
         <v>112.5482854560172</v>
       </c>
       <c r="E155" s="2">
-        <v>0.004707228721884385</v>
+        <v>0.004707228721884386</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -4498,7 +4498,7 @@
         <v>106.0521506490093</v>
       </c>
       <c r="E156" s="2">
-        <v>0.01460903021530449</v>
+        <v>0.0146090302153045</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -4515,7 +4515,7 @@
         <v>102.985061818783</v>
       </c>
       <c r="E157" s="2">
-        <v>0.003193449130731065</v>
+        <v>0.003193449130731066</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -4532,7 +4532,7 @@
         <v>111.8825634168241</v>
       </c>
       <c r="E158" s="2">
-        <v>0.002042556037980257</v>
+        <v>0.002042556037980258</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -4549,7 +4549,7 @@
         <v>121.200355942586</v>
       </c>
       <c r="E159" s="2">
-        <v>0.005652473585928469</v>
+        <v>0.005652473585928471</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -4560,7 +4560,7 @@
         <v>322</v>
       </c>
       <c r="C160" s="2">
-        <v>0.00461132237403101</v>
+        <v>0.004611322374031009</v>
       </c>
       <c r="D160" s="2">
         <v>110.3670819001615</v>
@@ -4583,7 +4583,7 @@
         <v>102.3390300089244</v>
       </c>
       <c r="E161" s="2">
-        <v>0.004487956700820628</v>
+        <v>0.004487956700820629</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -4600,7 +4600,7 @@
         <v>123.5756630600025</v>
       </c>
       <c r="E162" s="2">
-        <v>0.00326119198151652</v>
+        <v>0.003261191981516522</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -4617,7 +4617,7 @@
         <v>104.1162443810259</v>
       </c>
       <c r="E163" s="2">
-        <v>0.002092316115213712</v>
+        <v>0.002092316115213713</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -4634,7 +4634,7 @@
         <v>116.7889143285294</v>
       </c>
       <c r="E164" s="2">
-        <v>0.002031651231970149</v>
+        <v>0.00203165123197015</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -4651,7 +4651,7 @@
         <v>101.617442342346</v>
       </c>
       <c r="E165" s="2">
-        <v>0.002469508103024141</v>
+        <v>0.002469508103024143</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -4668,7 +4668,7 @@
         <v>117.3352509416753</v>
       </c>
       <c r="E166" s="2">
-        <v>0.002976271920634674</v>
+        <v>0.002976271920634676</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -4685,7 +4685,7 @@
         <v>118.4440206437201</v>
       </c>
       <c r="E167" s="2">
-        <v>0.001561679012608615</v>
+        <v>0.001561679012608616</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -4702,7 +4702,7 @@
         <v>118.4440206437201</v>
       </c>
       <c r="E168" s="2">
-        <v>0.005697231293520728</v>
+        <v>0.005697231293520731</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -4713,13 +4713,13 @@
         <v>340</v>
       </c>
       <c r="C169" s="2">
-        <v>0.003897798195780221</v>
+        <v>0.00389779819578022</v>
       </c>
       <c r="D169" s="2">
         <v>100.8199980162666</v>
       </c>
       <c r="E169" s="2">
-        <v>0.003897798195780219</v>
+        <v>0.00389779819578022</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -4730,7 +4730,7 @@
         <v>342</v>
       </c>
       <c r="C170" s="2">
-        <v>0.002520586117202039</v>
+        <v>0.002520586117202038</v>
       </c>
       <c r="D170" s="2">
         <v>109.8211612559688</v>
@@ -4753,7 +4753,7 @@
         <v>114.8908903922698</v>
       </c>
       <c r="E171" s="2">
-        <v>0.003876239697695962</v>
+        <v>0.003876239697695964</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -4770,7 +4770,7 @@
         <v>116.0636847723118</v>
       </c>
       <c r="E172" s="2">
-        <v>0.003265253531710844</v>
+        <v>0.003265253531710846</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -4781,13 +4781,13 @@
         <v>348</v>
       </c>
       <c r="C173" s="2">
-        <v>0.005640666773651918</v>
+        <v>0.005640666773651919</v>
       </c>
       <c r="D173" s="2">
         <v>113.2392440696313</v>
       </c>
       <c r="E173" s="2">
-        <v>0.005640666773651915</v>
+        <v>0.005640666773651919</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -4821,7 +4821,7 @@
         <v>125.2045137418748</v>
       </c>
       <c r="E175" s="2">
-        <v>0.003210377619806594</v>
+        <v>0.003210377619806596</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -4838,7 +4838,7 @@
         <v>120.4989626511365</v>
       </c>
       <c r="E176" s="2">
-        <v>0.001923802966575533</v>
+        <v>0.001923802966575534</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -4855,7 +4855,7 @@
         <v>114.3494643625409</v>
       </c>
       <c r="E177" s="2">
-        <v>0.002056639809080609</v>
+        <v>0.00205663980908061</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -4866,13 +4866,13 @@
         <v>358</v>
       </c>
       <c r="C178" s="2">
-        <v>0.002561838458158481</v>
+        <v>0.002561838458158482</v>
       </c>
       <c r="D178" s="2">
         <v>124.5985553688324</v>
       </c>
       <c r="E178" s="2">
-        <v>0.002561838458158479</v>
+        <v>0.002561838458158482</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -4883,7 +4883,7 @@
         <v>360</v>
       </c>
       <c r="C179" s="2">
-        <v>0.002057576947323736</v>
+        <v>0.002057576947323735</v>
       </c>
       <c r="D179" s="2">
         <v>101.8221212005676</v>
@@ -4906,7 +4906,7 @@
         <v>102.3870666822451</v>
       </c>
       <c r="E180" s="2">
-        <v>0.0004626212865031775</v>
+        <v>0.0004626212865031777</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -4917,13 +4917,13 @@
         <v>364</v>
       </c>
       <c r="C181" s="2">
-        <v>0.00273576606798322</v>
+        <v>0.002735766067983221</v>
       </c>
       <c r="D181" s="2">
         <v>142.9717145523893</v>
       </c>
       <c r="E181" s="2">
-        <v>0.002735766067983219</v>
+        <v>0.002735766067983221</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -4940,7 +4940,7 @@
         <v>132.4970879469516</v>
       </c>
       <c r="E182" s="2">
-        <v>0.003939332588984336</v>
+        <v>0.003939332588984337</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -4957,7 +4957,7 @@
         <v>136.9414505736339</v>
       </c>
       <c r="E183" s="2">
-        <v>0.002883412369657908</v>
+        <v>0.002883412369657909</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -4974,7 +4974,7 @@
         <v>119.7284240132797</v>
       </c>
       <c r="E184" s="2">
-        <v>0.001748404572668814</v>
+        <v>0.001748404572668815</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -4991,7 +4991,7 @@
         <v>108.9425392318104</v>
       </c>
       <c r="E185" s="2">
-        <v>0.009409166407254229</v>
+        <v>0.009409166407254232</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -5008,7 +5008,7 @@
         <v>128.5651319546794</v>
       </c>
       <c r="E186" s="2">
-        <v>0.001834754874827224</v>
+        <v>0.001834754874827225</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -5019,13 +5019,13 @@
         <v>376</v>
       </c>
       <c r="C187" s="2">
-        <v>0.0008730282403390268</v>
+        <v>0.0008730282403390269</v>
       </c>
       <c r="D187" s="2">
         <v>115.2976447895202</v>
       </c>
       <c r="E187" s="2">
-        <v>0.0008730282403390263</v>
+        <v>0.0008730282403390269</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -5042,7 +5042,7 @@
         <v>113.2250058515989</v>
       </c>
       <c r="E188" s="2">
-        <v>0.001598095106287384</v>
+        <v>0.001598095106287385</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -5053,13 +5053,13 @@
         <v>380</v>
       </c>
       <c r="C189" s="2">
-        <v>0.002557176015161539</v>
+        <v>0.002557176015161538</v>
       </c>
       <c r="D189" s="2">
         <v>131.4999827235525</v>
       </c>
       <c r="E189" s="2">
-        <v>0.002557176015161537</v>
+        <v>0.002557176015161538</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -5093,7 +5093,7 @@
         <v>152.0435564196542</v>
       </c>
       <c r="E191" s="2">
-        <v>0.008554624179176443</v>
+        <v>0.008554624179176447</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -5104,13 +5104,13 @@
         <v>386</v>
       </c>
       <c r="C192" s="2">
-        <v>0.003101335786287848</v>
+        <v>0.003101335786287847</v>
       </c>
       <c r="D192" s="2">
         <v>126.4417291515191</v>
       </c>
       <c r="E192" s="2">
-        <v>0.003101335786287846</v>
+        <v>0.003101335786287847</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -5121,13 +5121,13 @@
         <v>388</v>
       </c>
       <c r="C193" s="2">
-        <v>0.003285922341545626</v>
+        <v>0.003285922341545625</v>
       </c>
       <c r="D193" s="2">
         <v>133.6621489663754</v>
       </c>
       <c r="E193" s="2">
-        <v>0.003285922341545624</v>
+        <v>0.003285922341545625</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -5144,7 +5144,7 @@
         <v>118.4779191230055</v>
       </c>
       <c r="E194" s="2">
-        <v>0.002014072112219649</v>
+        <v>0.00201407211221965</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -5161,7 +5161,7 @@
         <v>109.3090670474812</v>
       </c>
       <c r="E195" s="2">
-        <v>0.001762929932485269</v>
+        <v>0.00176292993248527</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -5178,7 +5178,7 @@
         <v>134.7727798326113</v>
       </c>
       <c r="E196" s="2">
-        <v>0.003583294702672428</v>
+        <v>0.003583294702672429</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -5195,7 +5195,7 @@
         <v>144.8143846146146</v>
       </c>
       <c r="E197" s="2">
-        <v>0.00273218237658551</v>
+        <v>0.002732182376585512</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -5206,7 +5206,7 @@
         <v>398</v>
       </c>
       <c r="C198" s="2">
-        <v>0.004618988752594018</v>
+        <v>0.004618988752594016</v>
       </c>
       <c r="D198" s="2">
         <v>102.0397378720663</v>
@@ -5229,7 +5229,7 @@
         <v>104.6484752694456</v>
       </c>
       <c r="E199" s="2">
-        <v>0.00291338390316606</v>
+        <v>0.002913383903166062</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -5246,7 +5246,7 @@
         <v>109.9704332591837</v>
       </c>
       <c r="E200" s="2">
-        <v>0.002049793571875649</v>
+        <v>0.00204979357187565</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -5263,7 +5263,7 @@
         <v>115.9715994977748</v>
       </c>
       <c r="E201" s="2">
-        <v>0.00331092962431527</v>
+        <v>0.003310929624315272</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -5280,7 +5280,7 @@
         <v>112.8880432259372</v>
       </c>
       <c r="E202" s="2">
-        <v>0.006813014036090502</v>
+        <v>0.006813014036090505</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -5297,7 +5297,7 @@
         <v>112.551479720208</v>
       </c>
       <c r="E203" s="2">
-        <v>0.004452298522767925</v>
+        <v>0.004452298522767927</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -5314,7 +5314,7 @@
         <v>113.5612423327977</v>
       </c>
       <c r="E204" s="2">
-        <v>0.002242745856200222</v>
+        <v>0.002242745856200223</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -5331,7 +5331,7 @@
         <v>107.8677740599852</v>
       </c>
       <c r="E205" s="2">
-        <v>0.003585171719064257</v>
+        <v>0.003585171719064259</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -5345,10 +5345,10 @@
         <v>0.002359618710754059</v>
       </c>
       <c r="D206" s="2">
-        <v>148.2113345193274</v>
+        <v>148.2113345193275</v>
       </c>
       <c r="E206" s="2">
-        <v>0.002359618710754058</v>
+        <v>0.002359618710754059</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -5365,7 +5365,7 @@
         <v>147.9243809518905</v>
       </c>
       <c r="E207" s="2">
-        <v>0.005576436861479946</v>
+        <v>0.005576436861479949</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -5382,7 +5382,7 @@
         <v>116.0797230682434</v>
       </c>
       <c r="E208" s="2">
-        <v>0.00713052466890947</v>
+        <v>0.007130524668909474</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -5399,7 +5399,7 @@
         <v>108.28657017377</v>
       </c>
       <c r="E209" s="2">
-        <v>0.004816127660820616</v>
+        <v>0.004816127660820618</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -5416,7 +5416,7 @@
         <v>133.9454408331989</v>
       </c>
       <c r="E210" s="2">
-        <v>0.005657205498820687</v>
+        <v>0.00565720549882069</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -5433,7 +5433,7 @@
         <v>103.1672210782087</v>
       </c>
       <c r="E211" s="2">
-        <v>0.001942967650019651</v>
+        <v>0.001942967650019652</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -5450,7 +5450,7 @@
         <v>115.8309606806723</v>
       </c>
       <c r="E212" s="2">
-        <v>0.003100426153323277</v>
+        <v>0.003100426153323278</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -5467,7 +5467,7 @@
         <v>133.6256828128485</v>
       </c>
       <c r="E213" s="2">
-        <v>0.004905123667087442</v>
+        <v>0.004905123667087444</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -5484,7 +5484,7 @@
         <v>127.5215330804959</v>
       </c>
       <c r="E214" s="2">
-        <v>0.006674862763991394</v>
+        <v>0.006674862763991396</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -5501,7 +5501,7 @@
         <v>105.308241508552</v>
       </c>
       <c r="E215" s="2">
-        <v>0.01125331222004014</v>
+        <v>0.01125331222004015</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -5518,7 +5518,7 @@
         <v>104.7410527909654</v>
       </c>
       <c r="E216" s="2">
-        <v>0.003943683000181</v>
+        <v>0.003943683000181002</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -5535,7 +5535,7 @@
         <v>119.0421589053979</v>
       </c>
       <c r="E217" s="2">
-        <v>0.003131441992932657</v>
+        <v>0.003131441992932658</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -5552,7 +5552,7 @@
         <v>116.0213652278807</v>
       </c>
       <c r="E218" s="2">
-        <v>0.007901762268695416</v>
+        <v>0.00790176226869542</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -5569,7 +5569,7 @@
         <v>121.3086365639314</v>
       </c>
       <c r="E219" s="2">
-        <v>0.004522000989119678</v>
+        <v>0.004522000989119679</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -5586,7 +5586,7 @@
         <v>112.1123094239265</v>
       </c>
       <c r="E220" s="2">
-        <v>0.01014131342513254</v>
+        <v>0.01014131342513255</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -5603,7 +5603,7 @@
         <v>105.8233396810836</v>
       </c>
       <c r="E221" s="2">
-        <v>0.00911933737971217</v>
+        <v>0.009119337379712173</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -5614,13 +5614,13 @@
         <v>446</v>
       </c>
       <c r="C222" s="2">
-        <v>0.003433628848985228</v>
+        <v>0.003433628848985227</v>
       </c>
       <c r="D222" s="2">
         <v>120.2529853267684</v>
       </c>
       <c r="E222" s="2">
-        <v>0.003433628848985226</v>
+        <v>0.003433628848985227</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -5637,7 +5637,7 @@
         <v>120.347260246615</v>
       </c>
       <c r="E223" s="2">
-        <v>0.006218568967238964</v>
+        <v>0.006218568967238967</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -5648,13 +5648,13 @@
         <v>450</v>
       </c>
       <c r="C224" s="2">
-        <v>0.005172911408333307</v>
+        <v>0.005172911408333306</v>
       </c>
       <c r="D224" s="2">
         <v>113.8369996969351</v>
       </c>
       <c r="E224" s="2">
-        <v>0.005172911408333304</v>
+        <v>0.005172911408333306</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -5671,7 +5671,7 @@
         <v>147.6169305330523</v>
       </c>
       <c r="E225" s="2">
-        <v>0.001501360195453037</v>
+        <v>0.001501360195453038</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -5688,7 +5688,7 @@
         <v>118.0609831256961</v>
       </c>
       <c r="E226" s="2">
-        <v>0.01259572712756521</v>
+        <v>0.01259572712756522</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -5699,13 +5699,13 @@
         <v>456</v>
       </c>
       <c r="C227" s="2">
-        <v>0.003223219710010999</v>
+        <v>0.003223219710011</v>
       </c>
       <c r="D227" s="2">
         <v>102.1114870129703</v>
       </c>
       <c r="E227" s="2">
-        <v>0.003223219710010998</v>
+        <v>0.003223219710011</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -5716,13 +5716,13 @@
         <v>458</v>
       </c>
       <c r="C228" s="2">
-        <v>0.003063062324578662</v>
+        <v>0.003063062324578663</v>
       </c>
       <c r="D228" s="2">
         <v>103.3156397339718</v>
       </c>
       <c r="E228" s="2">
-        <v>0.003063062324578661</v>
+        <v>0.003063062324578663</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -5733,13 +5733,13 @@
         <v>460</v>
       </c>
       <c r="C229" s="2">
-        <v>0.008457019779584974</v>
+        <v>0.008457019779584976</v>
       </c>
       <c r="D229" s="2">
         <v>101.2299955546774</v>
       </c>
       <c r="E229" s="2">
-        <v>0.008457019779584971</v>
+        <v>0.008457019779584976</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -5750,13 +5750,13 @@
         <v>462</v>
       </c>
       <c r="C230" s="2">
-        <v>0.004381477542780259</v>
+        <v>0.00438147754278026</v>
       </c>
       <c r="D230" s="2">
         <v>100.7687482555976</v>
       </c>
       <c r="E230" s="2">
-        <v>0.004381477542780257</v>
+        <v>0.00438147754278026</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -5784,13 +5784,13 @@
         <v>466</v>
       </c>
       <c r="C232" s="2">
-        <v>0.0009792617142467259</v>
+        <v>0.0009792617142467257</v>
       </c>
       <c r="D232" s="2">
         <v>105.1249256836836</v>
       </c>
       <c r="E232" s="2">
-        <v>0.0009792617142467255</v>
+        <v>0.0009792617142467257</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -5801,13 +5801,13 @@
         <v>468</v>
       </c>
       <c r="C233" s="2">
-        <v>0.0007459128138547987</v>
+        <v>0.0007459128138547985</v>
       </c>
       <c r="D233" s="2">
         <v>106.1498940178463</v>
       </c>
       <c r="E233" s="2">
-        <v>0.0007459128138547984</v>
+        <v>0.0007459128138547985</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -5824,7 +5824,7 @@
         <v>100.2049998752557</v>
       </c>
       <c r="E234" s="2">
-        <v>0.002612091938062683</v>
+        <v>0.002612091938062684</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -5841,7 +5841,7 @@
         <v>100.7687482555976</v>
       </c>
       <c r="E235" s="2">
-        <v>0.004456026724644127</v>
+        <v>0.004456026724644129</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -5858,7 +5858,7 @@
         <v>100.8199980162666</v>
       </c>
       <c r="E236" s="2">
-        <v>0.004563721080600523</v>
+        <v>0.004563721080600524</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -5886,13 +5886,13 @@
         <v>478</v>
       </c>
       <c r="C238" s="2">
-        <v>0.004256005670837606</v>
+        <v>0.004256005670837607</v>
       </c>
       <c r="D238" s="2">
         <v>133.3100240041985</v>
       </c>
       <c r="E238" s="2">
-        <v>0.004256005670837604</v>
+        <v>0.004256005670837607</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -5909,7 +5909,7 @@
         <v>100.6662486884258</v>
       </c>
       <c r="E239" s="2">
-        <v>0.005447997062165003</v>
+        <v>0.005447997062165005</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -5926,7 +5926,7 @@
         <v>106.1498940178463</v>
       </c>
       <c r="E240" s="2">
-        <v>0.003358020759469275</v>
+        <v>0.003358020759469276</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -5943,7 +5943,7 @@
         <v>102.6906040309921</v>
       </c>
       <c r="E241" s="2">
-        <v>0.003778263799348651</v>
+        <v>0.003778263799348652</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -5954,13 +5954,13 @@
         <v>486</v>
       </c>
       <c r="C242" s="2">
-        <v>0.0008549570768601019</v>
+        <v>0.0008549570768601017</v>
       </c>
       <c r="D242" s="2">
         <v>101.0249969067062</v>
       </c>
       <c r="E242" s="2">
-        <v>0.0008549570768601014</v>
+        <v>0.0008549570768601017</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -5988,13 +5988,13 @@
         <v>490</v>
       </c>
       <c r="C244" s="2">
-        <v>0.007704079652770596</v>
+        <v>0.007704079652770597</v>
       </c>
       <c r="D244" s="2">
         <v>100.2049998752557</v>
       </c>
       <c r="E244" s="2">
-        <v>0.007704079652770593</v>
+        <v>0.007704079652770597</v>
       </c>
     </row>
   </sheetData>
